--- a/AGD20K semantically-expanded test texts.xlsx
+++ b/AGD20K semantically-expanded test texts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\OpenDI-release\repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DD433B-AA9E-4A78-B426-984720B8095A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1EF927-2D8F-46CC-B210-85DF5ABCEF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test texts" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="491">
   <si>
     <t>Object</t>
   </si>
@@ -820,12 +820,6 @@
     <t>Carefully open the suitcase to reveal what is inside</t>
   </si>
   <si>
-    <t>Pack</t>
-  </si>
-  <si>
-    <t>Put belongings inside</t>
-  </si>
-  <si>
     <t>Pack the suitcase</t>
   </si>
   <si>
@@ -1135,9 +1129,6 @@
     <t>Swing</t>
   </si>
   <si>
-    <t>Move in an arc</t>
-  </si>
-  <si>
     <t>Swing the badminton racket</t>
   </si>
   <si>
@@ -1219,12 +1210,6 @@
     <t>Talk to someone on the cell phone during calls</t>
   </si>
   <si>
-    <t>Text_on</t>
-  </si>
-  <si>
-    <t>Compose a message</t>
-  </si>
-  <si>
     <t>Text on the cell phone</t>
   </si>
   <si>
@@ -1421,12 +1406,6 @@
   </si>
   <si>
     <t>Pen</t>
-  </si>
-  <si>
-    <t>Write</t>
-  </si>
-  <si>
-    <t>Form written words</t>
   </si>
   <si>
     <t>Write with the pen</t>
@@ -1503,6 +1482,42 @@
   </si>
   <si>
     <t>Put the snowboard on table</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Swing</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Write</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Swing forward</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Write down</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Text_on</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Send a message</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wrap</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carry</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1510,7 +1525,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1537,6 +1552,11 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1569,12 +1589,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1886,9 +1909,9 @@
         <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1908,7 +1931,7 @@
       <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1928,7 +1951,7 @@
       <c r="B7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -1948,7 +1971,7 @@
       <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2163,7 +2186,7 @@
     </row>
     <row r="19" spans="1:6" ht="52.05" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>93</v>
@@ -2369,7 +2392,7 @@
         <v>127</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>133</v>
@@ -2549,10 +2572,10 @@
         <v>144</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>147</v>
@@ -2572,13 +2595,13 @@
         <v>145</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="52.05" customHeight="1">
@@ -2629,16 +2652,16 @@
         <v>144</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="52.05" customHeight="1">
@@ -2658,7 +2681,7 @@
         <v>147</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="52.05" customHeight="1">
@@ -2735,7 +2758,7 @@
         <v>179</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>180</v>
@@ -2755,7 +2778,7 @@
         <v>181</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>182</v>
@@ -2772,7 +2795,7 @@
         <v>145</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>147</v>
@@ -2783,13 +2806,13 @@
     </row>
     <row r="50" spans="1:6" ht="52.05" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>184</v>
@@ -3226,19 +3249,19 @@
         <v>86</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="52.05" customHeight="1">
@@ -3246,19 +3269,19 @@
         <v>57</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="52.05" customHeight="1">
@@ -3266,19 +3289,19 @@
         <v>63</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D74" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="52.05" customHeight="1">
@@ -3286,19 +3309,19 @@
         <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="52.05" customHeight="1">
@@ -3306,19 +3329,19 @@
         <v>71</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="52.05" customHeight="1">
@@ -3326,19 +3349,19 @@
         <v>30</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="52.05" customHeight="1">
@@ -3346,19 +3369,19 @@
         <v>86</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="52.05" customHeight="1">
@@ -3366,19 +3389,19 @@
         <v>92</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="F79" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="52.05" customHeight="1">
@@ -3386,19 +3409,19 @@
         <v>98</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="52.05" customHeight="1">
@@ -3406,99 +3429,99 @@
         <v>101</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D81" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="52.05" customHeight="1">
       <c r="A82" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="52.05" customHeight="1">
       <c r="A83" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D83" s="1" t="s">
+      <c r="F83" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="52.05" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="F84" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="52.05" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D85" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="52.05" customHeight="1">
@@ -3506,19 +3529,19 @@
         <v>98</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="F86" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="52.05" customHeight="1">
@@ -3526,19 +3549,19 @@
         <v>101</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D87" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="52.05" customHeight="1">
@@ -3546,19 +3569,19 @@
         <v>215</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="F88" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="52.05" customHeight="1">
@@ -3566,59 +3589,59 @@
         <v>221</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D89" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="52.05" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D90" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="52.05" customHeight="1">
       <c r="A91" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="D91" s="1" t="s">
+      <c r="F91" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="52.05" customHeight="1">
@@ -3626,39 +3649,39 @@
         <v>225</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="52.05" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D93" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="52.05" customHeight="1">
@@ -3666,19 +3689,19 @@
         <v>24</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="52.05" customHeight="1">
@@ -3686,19 +3709,19 @@
         <v>38</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D95" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="52.05" customHeight="1">
@@ -3706,19 +3729,19 @@
         <v>165</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="52.05" customHeight="1">
@@ -3726,19 +3749,19 @@
         <v>75</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="52.05" customHeight="1">
@@ -3746,19 +3769,19 @@
         <v>161</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="F98" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="52.05" customHeight="1">
@@ -3766,19 +3789,19 @@
         <v>149</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="F99" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="52.05" customHeight="1">
@@ -3786,19 +3809,19 @@
         <v>132</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>371</v>
+        <v>484</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="52.05" customHeight="1">
@@ -3806,19 +3829,19 @@
         <v>168</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>371</v>
+        <v>484</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="52.05" customHeight="1">
@@ -3826,159 +3849,159 @@
         <v>140</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>371</v>
+        <v>484</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="52.05" customHeight="1">
       <c r="A103" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="F103" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="52.05" customHeight="1">
       <c r="A104" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="52.05" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="F105" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="52.05" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>399</v>
+        <v>486</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>400</v>
+        <v>488</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="52.05" customHeight="1">
       <c r="A107" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="52.05" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C108" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="52.05" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="52.05" customHeight="1">
@@ -3986,39 +4009,39 @@
         <v>42</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="52.05" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="52.05" customHeight="1">
@@ -4026,59 +4049,59 @@
         <v>48</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="52.05" customHeight="1">
       <c r="A113" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="52.05" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C114" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>435</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="52.05" customHeight="1">
@@ -4086,19 +4109,19 @@
         <v>161</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="52.05" customHeight="1">
@@ -4106,19 +4129,19 @@
         <v>67</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="F116" s="1" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="52.05" customHeight="1">
@@ -4126,19 +4149,19 @@
         <v>98</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="52.05" customHeight="1">
@@ -4146,19 +4169,19 @@
         <v>165</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="52.05" customHeight="1">
@@ -4166,19 +4189,19 @@
         <v>75</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="52.05" customHeight="1">
@@ -4186,19 +4209,19 @@
         <v>71</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="52.05" customHeight="1">
@@ -4206,19 +4229,19 @@
         <v>18</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="52.05" customHeight="1">
@@ -4226,39 +4249,39 @@
         <v>101</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="52.05" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
